--- a/program/산출물양식/w2/제출본/[기획] WBS_2차_여행.xlsx
+++ b/program/산출물양식/w2/제출본/[기획] WBS_2차_여행.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>고객 언어로 링크·알림을 생성하는 방식 확정</t>
+          <t>여행계획서 내용·알림을 고객 언어로 생성하는 방식 확정</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>여행 규정 RAG 자료 교체 및 판정 규칙 정리</t>
+          <t>여행 규정 검색·생성용 자료 교체 및 판정 규칙 정리</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>분류 설정 도달성 CI·기동 검사</t>
+          <t>분류 설정에 따른 담당 모듈 연결을 자동 통합 검사와 서버 시작 시 검사로 검증</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Routes 경로·대중교통 조회 연동</t>
+          <t>경로·대중교통 조회 연동</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>여행 Team 등록 및 통지 문구 적용</t>
+          <t>여행 업무 모듈 등록 및 통지 문구 적용</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Activity 계약 및 기능 선택 구현</t>
+          <t>액티비티 모듈의 입출력 규약 및 기능 선택 구현</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Activity 단위·계약 테스트</t>
+          <t>액티비티 모듈 단위 테스트 및 입출력 규약 검증</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Dining 단위·계약 테스트</t>
+          <t>요식 모듈 단위 테스트 및 입출력 규약 검증</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Mobility 단위·계약 테스트</t>
+          <t>이동 모듈 단위 테스트 및 입출력 규약 검증</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>예약 인계 기능 선택 구현</t>
+          <t>예약 인계 기능 선택 구현 (MVP 다음)</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>예약 대조 및 공급자 등급 연결</t>
+          <t>예약 대조 및 공급자 등급 연결 (MVP 다음)</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>실제 업체 예약 변경 링크 생성</t>
+          <t>실제 업체 예약 변경 링크 생성 (MVP 다음)</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>일정·업체 예약 상태 분리 관리</t>
+          <t>일정·업체 예약 상태 분리 관리 (MVP 다음)</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>시뮬레이션 공급자 실행 허용 여부 검사 구현</t>
+          <t>시뮬레이션 공급자 실행 허용 여부 검사 구현 (MVP 다음)</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>공급자 자동 실행 차단 아키텍처 테스트</t>
+          <t>공급자 자동 실행 차단 아키텍처 테스트 (MVP 다음)</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>시연용 위임 범위 저장 및 대조</t>
+          <t>시연용 위임 범위 저장 및 대조 (MVP 다음)</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>시연용 Mock 공급자 커넥터 구현</t>
+          <t>시연용 모의 공급자 연동 모듈 구현 (MVP 다음)</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>시연용 Mock 예약 자동 실행 연결</t>
+          <t>시연용 모의 예약 자동 실행 연결 (MVP 다음)</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>시연용 자동 실행 감사 기록 구현</t>
+          <t>시연용 자동 실행 감사 기록 구현 (MVP 다음)</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>위임 철회 시 실행 정지 및 보상 처리</t>
+          <t>위임 철회 시 실행 정지 및 보상 처리 (MVP 다음)</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>관측·변화 저장 재사용 및 변화 비교</t>
+          <t>관측 결과·변화 기록 저장 및 재사용, 이전 관측 결과와 비교</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>한 Case 다중 Team 실행 연결</t>
+          <t>한 사건에서 여러 업무 모듈을 실행하도록 연결</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>일정 변경·통지 원자적 반영 구현</t>
+          <t>일정 변경과 통지 발송 대기열 등록의 일괄 저장 구현</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>여행·하루 시작 안내 문구틀</t>
+          <t>여행·하루 시작 안내 문구틀 작성</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>확정 시나리오(서울 하루 6사건) 시연 확정</t>
+          <t>확정 시나리오(서울 하루 6사건)의 시연 구성 확정</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>액티비티 모듈 스키마·ERD·아키텍처 설계</t>
+          <t>액티비티 모듈의 데이터 구조·개체 관계도·아키텍처 설계</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>조회 실패 시 대체 소스 전환 공통 처리 구현</t>
+          <t>조회 실패 시 대체 소스 전환 및 대체 조회 실패 시 서버 중단 공통 처리 구현</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>불확실한 후보 값의 단일안 선택 구현</t>
+          <t>후보 값이 불확실해도 최종안 하나를 선택하도록 구현</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>알림 번역 제외 항목(시각·금액·고유명사·예약번호) 검증</t>
+          <t>알림 원값 보존 항목(시각·날짜·금액·고유명사·예약번호) 검증</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>대체 소스·알림 언어 결정 시험</t>
+          <t>대체 소스 전환·대체 조회 실패 시 서버 중단·고객 언어 알림 생성 시험</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
@@ -7594,7 +7594,7 @@
       <c r="A127" s="1" t="n"/>
       <c r="B127" s="14" t="inlineStr">
         <is>
-          <t>근거: 구현계획서 v11 전문·09-10 결정, 알림 설계 문서, 비용과 수익구조 문서, DB 마이그레이션 010~013. 서울 1도시, 원본 한국어(링크·알림은 보낼 때 고객 언어로 생성, 결정 11·14), 접점 둘(API·여행계획서 링크), 화면 다섯을 기준으로 한다.</t>
+          <t>근거: 구현계획서 v11 전문·09-10 결정, 알림 설계 문서, 비용과 수익구조 문서, DB 마이그레이션 010~013. 서울 1도시, 한국어 원본, 접점 둘(API·여행계획서 링크), 화면 다섯을 기준으로 한다. 여행계획서 내용은 고객 언어로 제공하고, 알림은 보낼 때 고객 언어로 생성한다(결정 11·14).</t>
         </is>
       </c>
       <c r="C127" s="1" t="n"/>
@@ -7658,7 +7658,7 @@
       <c r="A129" s="1" t="n"/>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>일정이 밀리면 Team·이동, Team·요식 순으로 절삭을 검토한다. Activity·Booking Handoff·감시·묶음 조정·배달·여행계획서 링크·일정 안내는 유지한다. Mobility Team을 줄여도 전체 일정 검증과 출발 안내의 선행 조건인 Routes 조회는 남긴다.</t>
+          <t>일정이 밀리면 예약 인계(Booking Handoff — MVP 다음) 작업을 먼저 뒤로 민다. Activity·Dining·Mobility(MVP)·감시·묶음 조정·배달·여행계획서 링크·일정 안내는 유지한다. 전체 일정 검증과 출발 안내의 선행 조건인 Routes 조회는 남긴다.</t>
         </is>
       </c>
       <c r="C129" s="1" t="n"/>
@@ -7690,7 +7690,7 @@
       <c r="A130" s="1" t="n"/>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>010~013의 표 정의는 존재하지만 trips·itinerary_versions·watch_schedule은 아직 설계다. 경로·대중교통 조회와 자동 실행 게이트는 아직 구현 전이다. Routes 연결, 이동 시간 저장, 출발 역산 순서와 게이트·아키텍처 테스트, Mock 자동 실행 순서를 지킨다.</t>
+          <t>010~013의 표 정의는 존재하지만 trips·itinerary_versions·watch_schedule은 아직 설계다. 경로·대중교통 조회와 자동 실행 허용 여부 검사는 아직 구현 전이다. 경로 조회 연동, 이동 시간 저장, 출발 시각 역산 순서로 구현한다. 모의 예약 자동 실행은 실행 허용 여부 검사와 아키텍처 테스트를 마친 뒤 연결한다.</t>
         </is>
       </c>
       <c r="C130" s="1" t="n"/>
@@ -7722,7 +7722,7 @@
       <c r="A131" s="1" t="n"/>
       <c r="B131" s="14" t="inlineStr">
         <is>
-          <t>알림 수신·읽음은 제품 조건이 아니며 상태의 정본은 여행계획서 링크다. 직접 링크·알림은 보낼 때 고객 언어로 생성한다(결정 11·14). 여행 건당 Places·Routes 조회량, 인계 비율·처리 시간은 시연 데이터로 1차 측정하고 파일럿에서 다시 측정한다. 실제 업체 예약은 승인 경로이며 자동 실행은 Mock 한정 시연이다. DoD는 26항목(자동 20·아키텍처 테스트 4·측정 2)으로 판정한다.</t>
+          <t>알림 수신·읽음은 제품 조건이 아니며 상태의 정본은 여행계획서 링크다. 여행계획서 내용은 고객 언어로 제공하고, 알림은 보낼 때 고객 언어로 생성한다(결정 11·14). 여행 건당 장소·경로 조회량, 인계 비율·처리 시간은 시연 데이터로 1차 측정하고 파일럿에서 다시 측정한다. 실제 업체 예약 변경은 승인을 거치며, 자동 실행은 모의 공급자를 대상으로만 시연한다. 완료 여부는 26항목(자동 20·아키텍처 테스트 4·측정 2)으로 판정한다.</t>
         </is>
       </c>
       <c r="C131" s="1" t="n"/>

--- a/program/산출물양식/w2/제출본/[기획] WBS_2차_여행.xlsx
+++ b/program/산출물양식/w2/제출본/[기획] WBS_2차_여행.xlsx
@@ -6607,7 +6607,7 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>공급자 경계·위임 실행 완료 기준 시험</t>
+          <t>공급자 경계·위임 실행 완료 기준 시험 (MVP 다음 단계)</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>완료 기준 26항목의 검증 자료 정리</t>
+          <t>완료 기준 26항목의 검증 자료 정리(MVP 판정 18항목, DoD-14~21은 MVP 다음 단계)</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -7658,7 +7658,7 @@
       <c r="A129" s="1" t="n"/>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>일정이 밀리면 예약 인계(Booking Handoff — MVP 다음) 작업을 먼저 뒤로 민다. Activity·Dining·Mobility(MVP)·감시·묶음 조정·배달·여행계획서 링크·일정 안내는 유지한다. 전체 일정 검증과 출발 안내의 선행 조건인 Routes 조회는 남긴다.</t>
+          <t>일정이 밀리면 예약 인계(Booking Handoff: MVP 다음) 작업을 먼저 뒤로 민다. Activity·Dining·Mobility(MVP)·감시·묶음 조정·배달·여행계획서 링크·일정 안내는 유지한다. 전체 일정 검증과 출발 안내의 선행 조건인 Routes 조회는 남긴다.</t>
         </is>
       </c>
       <c r="C129" s="1" t="n"/>
@@ -7690,7 +7690,7 @@
       <c r="A130" s="1" t="n"/>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>010~013의 표 정의는 존재하지만 trips·itinerary_versions·watch_schedule은 아직 설계다. 경로·대중교통 조회와 자동 실행 허용 여부 검사는 아직 구현 전이다. 경로 조회 연동, 이동 시간 저장, 출발 시각 역산 순서로 구현한다. 모의 예약 자동 실행은 실행 허용 여부 검사와 아키텍처 테스트를 마친 뒤 연결한다.</t>
+          <t>010~013의 표 정의는 존재하지만 trips·itinerary_versions·watch_schedule은 아직 설계다. 경로·대중교통 조회와 자동 실행 허용 여부 검사는 아직 구현 전이다. 자동 실행 허용 여부 검사는 MVP 다음 단계 작업이다. 경로 조회 연동, 이동 시간 저장, 출발 시각 역산 순서로 구현한다. 모의 예약 자동 실행은 MVP 다음 단계에서 실행 허용 여부 검사와 아키텍처 테스트를 마친 뒤 연결한다.</t>
         </is>
       </c>
       <c r="C130" s="1" t="n"/>
@@ -7722,7 +7722,7 @@
       <c r="A131" s="1" t="n"/>
       <c r="B131" s="14" t="inlineStr">
         <is>
-          <t>알림 수신·읽음은 제품 조건이 아니며 상태의 정본은 여행계획서 링크다. 여행계획서 내용은 고객 언어로 제공하고, 알림은 보낼 때 고객 언어로 생성한다(결정 11·14). 여행 건당 장소·경로 조회량, 인계 비율·처리 시간은 시연 데이터로 1차 측정하고 파일럿에서 다시 측정한다. 실제 업체 예약 변경은 승인을 거치며, 자동 실행은 모의 공급자를 대상으로만 시연한다. 완료 여부는 26항목(자동 20·아키텍처 테스트 4·측정 2)으로 판정한다.</t>
+          <t>알림 수신·읽음은 제품 조건이 아니며 상태의 정본은 여행계획서 링크다. 여행계획서 내용은 고객 언어로 제공하고, 알림은 보낼 때 고객 언어로 생성한다(결정 11·14). 여행 건당 장소·경로 조회량, 인계 비율·처리 시간은 시연 데이터로 1차 측정하고 파일럿에서 다시 측정한다. MVP 다음 단계에서 실제 업체 예약 변경은 승인을 거치며, 자동 실행은 모의 공급자를 대상으로만 시연한다. 전체 완료 기준은 26항목(자동 20·아키텍처 테스트 4·측정 2)으로 유지한다. MVP 완료 여부는 DoD-14~21을 제외한 18항목으로 판정하며, DoD-14~21은 MVP 다음 단계에서 판정한다.</t>
         </is>
       </c>
       <c r="C131" s="1" t="n"/>

--- a/program/산출물양식/w2/제출본/[기획] WBS_2차_여행.xlsx
+++ b/program/산출물양식/w2/제출본/[기획] WBS_2차_여행.xlsx
@@ -7658,7 +7658,7 @@
       <c r="A129" s="1" t="n"/>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>일정이 밀리면 예약 인계(Booking Handoff: MVP 다음) 작업을 먼저 뒤로 민다. Activity·Dining·Mobility(MVP)·감시·묶음 조정·배달·여행계획서 링크·일정 안내는 유지한다. 전체 일정 검증과 출발 안내의 선행 조건인 Routes 조회는 남긴다.</t>
+          <t>예약 인계(Booking Handoff) 작업(Task 50~60·107)은 MVP 다음 단계라 MVP 판정에 들지 않는다. 일정이 밀리면 이 작업을 가장 먼저 뒤로 민다. Activity·Dining·Mobility(MVP)·감시·묶음 조정·배달·여행계획서 링크·일정 안내는 유지한다. 전체 일정 검증과 출발 안내의 선행 조건인 Routes 조회는 남긴다.</t>
         </is>
       </c>
       <c r="C129" s="1" t="n"/>
@@ -7722,7 +7722,7 @@
       <c r="A131" s="1" t="n"/>
       <c r="B131" s="14" t="inlineStr">
         <is>
-          <t>알림 수신·읽음은 제품 조건이 아니며 상태의 정본은 여행계획서 링크다. 여행계획서 내용은 고객 언어로 제공하고, 알림은 보낼 때 고객 언어로 생성한다(결정 11·14). 여행 건당 장소·경로 조회량, 인계 비율·처리 시간은 시연 데이터로 1차 측정하고 파일럿에서 다시 측정한다. MVP 다음 단계에서 실제 업체 예약 변경은 승인을 거치며, 자동 실행은 모의 공급자를 대상으로만 시연한다. 전체 완료 기준은 26항목(자동 20·아키텍처 테스트 4·측정 2)으로 유지한다. MVP 완료 여부는 DoD-14~21을 제외한 18항목으로 판정하며, DoD-14~21은 MVP 다음 단계에서 판정한다.</t>
+          <t>알림 수신·읽음은 제품 조건이 아니며 상태의 정본은 여행계획서 링크다. 여행계획서 내용은 고객 언어로 제공하고, 알림은 보낼 때 고객 언어로 생성한다(결정 11·14). 여행 건당 장소·경로 조회량, 인계 비율·처리 시간은 시연 데이터로 1차 측정하고 파일럿에서 다시 측정한다. 실제 업체 예약 변경은 언제나 승인을 거친다. 모의 공급자 대상 자동 실행 시연은 MVP 다음 단계에서 한다. 전체 완료 기준은 26항목(자동 20·아키텍처 테스트 4·측정 2)으로 유지한다. MVP 완료 여부는 DoD-14~21을 제외한 18항목으로 판정하며, DoD-14~21은 MVP 다음 단계에서 판정한다.</t>
         </is>
       </c>
       <c r="C131" s="1" t="n"/>
